--- a/data/processed/01_UC_Service_Centre_Reference.xlsx
+++ b/data/processed/01_UC_Service_Centre_Reference.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faith\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faith\Documents\UC_Service_Centre_Analysis\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9033B9B-6819-4E14-B4DA-404ECBC42775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E235C0D1-62C3-4683-8C58-C6B823519840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Service Centres" sheetId="1" r:id="rId1"/>
@@ -799,7 +799,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -814,6 +814,60 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="8" tint="0.59999389629810485"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8" tint="0.59999389629810485"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="0.59999389629810485"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="2">
@@ -947,7 +1001,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -956,9 +1010,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -974,9 +1025,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -984,9 +1032,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1001,13 +1046,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1016,37 +1055,83 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
     <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
+        <color theme="8"/>
       </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1054,8 +1139,64 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1070,7 +1211,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color rgb="FF1F2937"/>
+        <color rgb="FFFF0000"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
@@ -1082,10 +1223,10 @@
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1145,314 +1286,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color rgb="FF1F2937"/>
+        <color theme="8" tint="0.59999389629810485"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1564,11 +1402,10 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color rgb="FF1F2937"/>
+        <color rgb="FFFF0000"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1576,6 +1413,51 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1618,6 +1500,164 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1657,6 +1697,78 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1682,41 +1794,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ServiceCentres" displayName="ServiceCentres" ref="A1:H19" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ServiceCentres" displayName="ServiceCentres" ref="A1:H19" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Centre_ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Centre_Name" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Region_ID" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Region_Name" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Centre_ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Centre_Name" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Region_ID" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Region_Name" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Capacity_Band" dataDxfId="18"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Target_Processing_Days" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Operational_Lead_Code" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Opened_Date" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Operational_Lead_Code" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Opened_Date" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Regions" displayName="Regions" ref="A1:D7" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="14" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Regions" displayName="Regions" ref="A1:D7" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Region_ID" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Region_ID" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Region_Name" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Directorate" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Reporting_Group" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Directorate" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Reporting_Group" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ReportingCalendar" displayName="ReportingCalendar" ref="A1:E158" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ReportingCalendar" displayName="ReportingCalendar" ref="A1:E158" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Week_ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Week_Start" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Week_End" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quarter" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Reporting_Year" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Week_ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Week_Start" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Week_End" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quarter" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Reporting_Year" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1920,9 +2032,9 @@
   <dimension ref="A1:H158"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.0625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.0625" style="27" customWidth="1"/>
     <col min="2" max="2" width="20.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.9375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.9375" style="32" customWidth="1"/>
     <col min="4" max="4" width="20.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="18.0625" style="3" customWidth="1"/>
     <col min="6" max="6" width="22.625" style="3" customWidth="1"/>
@@ -1931,1470 +2043,1470 @@
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" s="7" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>10</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="19">
         <v>42370</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>10</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="19">
         <v>42827</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>12</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="19">
         <v>43284</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A5" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>10</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="19">
         <v>43742</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>10</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="19">
         <v>43835</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A7" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="19">
         <v>44292</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A8" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>10</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="19">
         <v>44749</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A9" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>10</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="19">
         <v>42651</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A10" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>12</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="19">
         <v>42744</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A11" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <v>10</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="19">
         <v>43200</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A12" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>10</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="19">
         <v>43657</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A13" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <v>12</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="19">
         <v>44116</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A14" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>10</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="19">
         <v>44209</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A15" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <v>10</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="19">
         <v>44665</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A16" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="7">
         <v>12</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="19">
         <v>42566</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A17" s="13" t="s">
+    <row r="17" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A17" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="7">
         <v>10</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="19">
         <v>43024</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A18" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="7">
         <v>10</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="19">
         <v>43117</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A19" s="17" t="s">
+    <row r="19" spans="1:8" s="7" customFormat="1" ht="18" customHeight="1">
+      <c r="A19" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="15">
         <v>12</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="20">
         <v>43573</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1">
-      <c r="A20" s="1"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1">
-      <c r="A21" s="1"/>
+      <c r="A21" s="26"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="C21" s="31"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1">
-      <c r="A22" s="1"/>
+      <c r="A22" s="26"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="C22" s="31"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1">
-      <c r="A23" s="1"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="C23" s="31"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1">
-      <c r="A24" s="1"/>
+      <c r="A24" s="26"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="C24" s="31"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1">
-      <c r="A25" s="1"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="C25" s="31"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1">
-      <c r="A26" s="1"/>
+      <c r="A26" s="26"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="C26" s="31"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1">
-      <c r="A27" s="1"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1">
-      <c r="A28" s="1"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="C28" s="31"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1">
-      <c r="A29" s="1"/>
+      <c r="A29" s="26"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="C29" s="31"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1">
-      <c r="A30" s="1"/>
+      <c r="A30" s="26"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+      <c r="C30" s="31"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1">
-      <c r="A31" s="1"/>
+      <c r="A31" s="26"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
+      <c r="C31" s="31"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:8" ht="18" customHeight="1">
-      <c r="A32" s="1"/>
+      <c r="A32" s="26"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="C32" s="31"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1">
-      <c r="A33" s="1"/>
+      <c r="A33" s="26"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="C33" s="31"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1">
-      <c r="A34" s="1"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="1"/>
+      <c r="A35" s="26"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+      <c r="C35" s="31"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1">
-      <c r="A36" s="1"/>
+      <c r="A36" s="26"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1">
-      <c r="A37" s="1"/>
+      <c r="A37" s="26"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="C37" s="31"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1">
-      <c r="A38" s="1"/>
+      <c r="A38" s="26"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
+      <c r="C38" s="31"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1">
-      <c r="A39" s="1"/>
+      <c r="A39" s="26"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
+      <c r="C39" s="31"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1">
-      <c r="A40" s="1"/>
+      <c r="A40" s="26"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
+      <c r="C40" s="31"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1">
-      <c r="A41" s="1"/>
+      <c r="A41" s="26"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1">
-      <c r="A42" s="1"/>
+      <c r="A42" s="26"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
+      <c r="C42" s="31"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1">
-      <c r="A43" s="1"/>
+      <c r="A43" s="26"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="C43" s="31"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1">
-      <c r="A44" s="1"/>
+      <c r="A44" s="26"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="C44" s="31"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1">
-      <c r="A45" s="1"/>
+      <c r="A45" s="26"/>
       <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
+      <c r="C45" s="31"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1">
-      <c r="A46" s="1"/>
+      <c r="A46" s="26"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
+      <c r="C46" s="31"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1">
-      <c r="A47" s="1"/>
+      <c r="A47" s="26"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
+      <c r="C47" s="31"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1">
-      <c r="A48" s="1"/>
+      <c r="A48" s="26"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
+      <c r="C48" s="31"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1">
-      <c r="A49" s="1"/>
+      <c r="A49" s="26"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
+      <c r="C49" s="31"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1">
-      <c r="A50" s="1"/>
+      <c r="A50" s="26"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
+      <c r="C50" s="31"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1">
-      <c r="A51" s="1"/>
+      <c r="A51" s="26"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="C51" s="31"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1">
-      <c r="A52" s="1"/>
+      <c r="A52" s="26"/>
       <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
+      <c r="C52" s="31"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5" ht="18" customHeight="1">
-      <c r="A53" s="1"/>
+      <c r="A53" s="26"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
+      <c r="C53" s="31"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1">
-      <c r="A54" s="1"/>
+      <c r="A54" s="26"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
+      <c r="C54" s="31"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1">
-      <c r="A55" s="1"/>
+      <c r="A55" s="26"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
+      <c r="C55" s="31"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1">
-      <c r="A56" s="1"/>
+      <c r="A56" s="26"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
+      <c r="C56" s="31"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1">
-      <c r="A57" s="1"/>
+      <c r="A57" s="26"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
+      <c r="C57" s="31"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1">
-      <c r="A58" s="1"/>
+      <c r="A58" s="26"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
+      <c r="C58" s="31"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
     </row>
     <row r="59" spans="1:5" ht="18" customHeight="1">
-      <c r="A59" s="1"/>
+      <c r="A59" s="26"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
+      <c r="C59" s="31"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1">
-      <c r="A60" s="1"/>
+      <c r="A60" s="26"/>
       <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
+      <c r="C60" s="31"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1">
-      <c r="A61" s="1"/>
+      <c r="A61" s="26"/>
       <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
+      <c r="C61" s="31"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1">
-      <c r="A62" s="1"/>
+      <c r="A62" s="26"/>
       <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
+      <c r="C62" s="31"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1">
-      <c r="A63" s="1"/>
+      <c r="A63" s="26"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
+      <c r="C63" s="31"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1">
-      <c r="A64" s="1"/>
+      <c r="A64" s="26"/>
       <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
+      <c r="C64" s="31"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
     </row>
     <row r="65" spans="1:5" ht="18" customHeight="1">
-      <c r="A65" s="1"/>
+      <c r="A65" s="26"/>
       <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="C65" s="31"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
     </row>
     <row r="66" spans="1:5" ht="18" customHeight="1">
-      <c r="A66" s="1"/>
+      <c r="A66" s="26"/>
       <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
+      <c r="C66" s="31"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
     </row>
     <row r="67" spans="1:5" ht="18" customHeight="1">
-      <c r="A67" s="1"/>
+      <c r="A67" s="26"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
+      <c r="C67" s="31"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
     </row>
     <row r="68" spans="1:5" ht="18" customHeight="1">
-      <c r="A68" s="1"/>
+      <c r="A68" s="26"/>
       <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
+      <c r="C68" s="31"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
     </row>
     <row r="69" spans="1:5" ht="18" customHeight="1">
-      <c r="A69" s="1"/>
+      <c r="A69" s="26"/>
       <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
+      <c r="C69" s="31"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
     </row>
     <row r="70" spans="1:5" ht="18" customHeight="1">
-      <c r="A70" s="1"/>
+      <c r="A70" s="26"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
+      <c r="C70" s="31"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
     </row>
     <row r="71" spans="1:5" ht="18" customHeight="1">
-      <c r="A71" s="1"/>
+      <c r="A71" s="26"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
+      <c r="C71" s="31"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
     </row>
     <row r="72" spans="1:5" ht="18" customHeight="1">
-      <c r="A72" s="1"/>
+      <c r="A72" s="26"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
+      <c r="C72" s="31"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
     </row>
     <row r="73" spans="1:5" ht="18" customHeight="1">
-      <c r="A73" s="1"/>
+      <c r="A73" s="26"/>
       <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
+      <c r="C73" s="31"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
     </row>
     <row r="74" spans="1:5" ht="18" customHeight="1">
-      <c r="A74" s="1"/>
+      <c r="A74" s="26"/>
       <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
+      <c r="C74" s="31"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
     </row>
     <row r="75" spans="1:5" ht="18" customHeight="1">
-      <c r="A75" s="1"/>
+      <c r="A75" s="26"/>
       <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
+      <c r="C75" s="31"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
     </row>
     <row r="76" spans="1:5" ht="18" customHeight="1">
-      <c r="A76" s="1"/>
+      <c r="A76" s="26"/>
       <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
+      <c r="C76" s="31"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
     </row>
     <row r="77" spans="1:5" ht="18" customHeight="1">
-      <c r="A77" s="1"/>
+      <c r="A77" s="26"/>
       <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
+      <c r="C77" s="31"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
     </row>
     <row r="78" spans="1:5" ht="18" customHeight="1">
-      <c r="A78" s="1"/>
+      <c r="A78" s="26"/>
       <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
+      <c r="C78" s="31"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
     </row>
     <row r="79" spans="1:5" ht="18" customHeight="1">
-      <c r="A79" s="1"/>
+      <c r="A79" s="26"/>
       <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
+      <c r="C79" s="31"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
     </row>
     <row r="80" spans="1:5" ht="18" customHeight="1">
-      <c r="A80" s="1"/>
+      <c r="A80" s="26"/>
       <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
+      <c r="C80" s="31"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
     </row>
     <row r="81" spans="1:5" ht="18" customHeight="1">
-      <c r="A81" s="1"/>
+      <c r="A81" s="26"/>
       <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
+      <c r="C81" s="31"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
     </row>
     <row r="82" spans="1:5" ht="18" customHeight="1">
-      <c r="A82" s="1"/>
+      <c r="A82" s="26"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
+      <c r="C82" s="31"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
     </row>
     <row r="83" spans="1:5" ht="18" customHeight="1">
-      <c r="A83" s="1"/>
+      <c r="A83" s="26"/>
       <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
+      <c r="C83" s="31"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
     </row>
     <row r="84" spans="1:5" ht="18" customHeight="1">
-      <c r="A84" s="1"/>
+      <c r="A84" s="26"/>
       <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
+      <c r="C84" s="31"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
     </row>
     <row r="85" spans="1:5" ht="18" customHeight="1">
-      <c r="A85" s="1"/>
+      <c r="A85" s="26"/>
       <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
+      <c r="C85" s="31"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
     </row>
     <row r="86" spans="1:5" ht="18" customHeight="1">
-      <c r="A86" s="1"/>
+      <c r="A86" s="26"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
+      <c r="C86" s="31"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
     </row>
     <row r="87" spans="1:5" ht="18" customHeight="1">
-      <c r="A87" s="1"/>
+      <c r="A87" s="26"/>
       <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
+      <c r="C87" s="31"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
     </row>
     <row r="88" spans="1:5" ht="18" customHeight="1">
-      <c r="A88" s="1"/>
+      <c r="A88" s="26"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
+      <c r="C88" s="31"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
     </row>
     <row r="89" spans="1:5" ht="18" customHeight="1">
-      <c r="A89" s="1"/>
+      <c r="A89" s="26"/>
       <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
+      <c r="C89" s="31"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
     </row>
     <row r="90" spans="1:5" ht="18" customHeight="1">
-      <c r="A90" s="1"/>
+      <c r="A90" s="26"/>
       <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
+      <c r="C90" s="31"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
     </row>
     <row r="91" spans="1:5" ht="18" customHeight="1">
-      <c r="A91" s="1"/>
+      <c r="A91" s="26"/>
       <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
+      <c r="C91" s="31"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
     </row>
     <row r="92" spans="1:5" ht="18" customHeight="1">
-      <c r="A92" s="1"/>
+      <c r="A92" s="26"/>
       <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
+      <c r="C92" s="31"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
     </row>
     <row r="93" spans="1:5" ht="18" customHeight="1">
-      <c r="A93" s="1"/>
+      <c r="A93" s="26"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
+      <c r="C93" s="31"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
     </row>
     <row r="94" spans="1:5" ht="18" customHeight="1">
-      <c r="A94" s="1"/>
+      <c r="A94" s="26"/>
       <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
+      <c r="C94" s="31"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
     </row>
     <row r="95" spans="1:5" ht="18" customHeight="1">
-      <c r="A95" s="1"/>
+      <c r="A95" s="26"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
+      <c r="C95" s="31"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
     </row>
     <row r="96" spans="1:5" ht="18" customHeight="1">
-      <c r="A96" s="1"/>
+      <c r="A96" s="26"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
+      <c r="C96" s="31"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
     </row>
     <row r="97" spans="1:5" ht="18" customHeight="1">
-      <c r="A97" s="1"/>
+      <c r="A97" s="26"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="C97" s="31"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
     </row>
     <row r="98" spans="1:5" ht="18" customHeight="1">
-      <c r="A98" s="1"/>
+      <c r="A98" s="26"/>
       <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
+      <c r="C98" s="31"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
     </row>
     <row r="99" spans="1:5" ht="18" customHeight="1">
-      <c r="A99" s="1"/>
+      <c r="A99" s="26"/>
       <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
+      <c r="C99" s="31"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
     </row>
     <row r="100" spans="1:5" ht="18" customHeight="1">
-      <c r="A100" s="1"/>
+      <c r="A100" s="26"/>
       <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
+      <c r="C100" s="31"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
     </row>
     <row r="101" spans="1:5" ht="18" customHeight="1">
-      <c r="A101" s="1"/>
+      <c r="A101" s="26"/>
       <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
+      <c r="C101" s="31"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
     </row>
     <row r="102" spans="1:5" ht="18" customHeight="1">
-      <c r="A102" s="1"/>
+      <c r="A102" s="26"/>
       <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
+      <c r="C102" s="31"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
     </row>
     <row r="103" spans="1:5" ht="18" customHeight="1">
-      <c r="A103" s="1"/>
+      <c r="A103" s="26"/>
       <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
+      <c r="C103" s="31"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
     </row>
     <row r="104" spans="1:5" ht="18" customHeight="1">
-      <c r="A104" s="1"/>
+      <c r="A104" s="26"/>
       <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
+      <c r="C104" s="31"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
     </row>
     <row r="105" spans="1:5" ht="18" customHeight="1">
-      <c r="A105" s="1"/>
+      <c r="A105" s="26"/>
       <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
+      <c r="C105" s="31"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
     </row>
     <row r="106" spans="1:5" ht="18" customHeight="1">
-      <c r="A106" s="1"/>
+      <c r="A106" s="26"/>
       <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
+      <c r="C106" s="31"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
     </row>
     <row r="107" spans="1:5" ht="18" customHeight="1">
-      <c r="A107" s="1"/>
+      <c r="A107" s="26"/>
       <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
+      <c r="C107" s="31"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
     </row>
     <row r="108" spans="1:5" ht="18" customHeight="1">
-      <c r="A108" s="1"/>
+      <c r="A108" s="26"/>
       <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
+      <c r="C108" s="31"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
     </row>
     <row r="109" spans="1:5" ht="18" customHeight="1">
-      <c r="A109" s="1"/>
+      <c r="A109" s="26"/>
       <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
+      <c r="C109" s="31"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
     </row>
     <row r="110" spans="1:5" ht="18" customHeight="1">
-      <c r="A110" s="1"/>
+      <c r="A110" s="26"/>
       <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
+      <c r="C110" s="31"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
     </row>
     <row r="111" spans="1:5" ht="18" customHeight="1">
-      <c r="A111" s="1"/>
+      <c r="A111" s="26"/>
       <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
+      <c r="C111" s="31"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
     </row>
     <row r="112" spans="1:5" ht="18" customHeight="1">
-      <c r="A112" s="1"/>
+      <c r="A112" s="26"/>
       <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
+      <c r="C112" s="31"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5" ht="18" customHeight="1">
-      <c r="A113" s="1"/>
+      <c r="A113" s="26"/>
       <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
+      <c r="C113" s="31"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
     </row>
     <row r="114" spans="1:5" ht="18" customHeight="1">
-      <c r="A114" s="1"/>
+      <c r="A114" s="26"/>
       <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
+      <c r="C114" s="31"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
     </row>
     <row r="115" spans="1:5" ht="18" customHeight="1">
-      <c r="A115" s="1"/>
+      <c r="A115" s="26"/>
       <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
+      <c r="C115" s="31"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
     </row>
     <row r="116" spans="1:5" ht="18" customHeight="1">
-      <c r="A116" s="1"/>
+      <c r="A116" s="26"/>
       <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
+      <c r="C116" s="31"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
     </row>
     <row r="117" spans="1:5" ht="18" customHeight="1">
-      <c r="A117" s="1"/>
+      <c r="A117" s="26"/>
       <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
+      <c r="C117" s="31"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
     </row>
     <row r="118" spans="1:5" ht="18" customHeight="1">
-      <c r="A118" s="1"/>
+      <c r="A118" s="26"/>
       <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
+      <c r="C118" s="31"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
     </row>
     <row r="119" spans="1:5" ht="18" customHeight="1">
-      <c r="A119" s="1"/>
+      <c r="A119" s="26"/>
       <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
+      <c r="C119" s="31"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
     </row>
     <row r="120" spans="1:5" ht="18" customHeight="1">
-      <c r="A120" s="1"/>
+      <c r="A120" s="26"/>
       <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
+      <c r="C120" s="31"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
     </row>
     <row r="121" spans="1:5" ht="18" customHeight="1">
-      <c r="A121" s="1"/>
+      <c r="A121" s="26"/>
       <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
+      <c r="C121" s="31"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
     </row>
     <row r="122" spans="1:5" ht="18" customHeight="1">
-      <c r="A122" s="1"/>
+      <c r="A122" s="26"/>
       <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
+      <c r="C122" s="31"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
     </row>
     <row r="123" spans="1:5" ht="18" customHeight="1">
-      <c r="A123" s="1"/>
+      <c r="A123" s="26"/>
       <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
+      <c r="C123" s="31"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
     </row>
     <row r="124" spans="1:5" ht="18" customHeight="1">
-      <c r="A124" s="1"/>
+      <c r="A124" s="26"/>
       <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
+      <c r="C124" s="31"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
     </row>
     <row r="125" spans="1:5" ht="18" customHeight="1">
-      <c r="A125" s="1"/>
+      <c r="A125" s="26"/>
       <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
+      <c r="C125" s="31"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:5" ht="18" customHeight="1">
-      <c r="A126" s="1"/>
+      <c r="A126" s="26"/>
       <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
+      <c r="C126" s="31"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5" ht="18" customHeight="1">
-      <c r="A127" s="1"/>
+      <c r="A127" s="26"/>
       <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
+      <c r="C127" s="31"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
     </row>
     <row r="128" spans="1:5" ht="18" customHeight="1">
-      <c r="A128" s="1"/>
+      <c r="A128" s="26"/>
       <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
+      <c r="C128" s="31"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5" ht="18" customHeight="1">
-      <c r="A129" s="1"/>
+      <c r="A129" s="26"/>
       <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
+      <c r="C129" s="31"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
     </row>
     <row r="130" spans="1:5" ht="18" customHeight="1">
-      <c r="A130" s="1"/>
+      <c r="A130" s="26"/>
       <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
+      <c r="C130" s="31"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
     </row>
     <row r="131" spans="1:5" ht="18" customHeight="1">
-      <c r="A131" s="1"/>
+      <c r="A131" s="26"/>
       <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
+      <c r="C131" s="31"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
     </row>
     <row r="132" spans="1:5" ht="18" customHeight="1">
-      <c r="A132" s="1"/>
+      <c r="A132" s="26"/>
       <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
+      <c r="C132" s="31"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
     </row>
     <row r="133" spans="1:5" ht="18" customHeight="1">
-      <c r="A133" s="1"/>
+      <c r="A133" s="26"/>
       <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
+      <c r="C133" s="31"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
     </row>
     <row r="134" spans="1:5" ht="18" customHeight="1">
-      <c r="A134" s="1"/>
+      <c r="A134" s="26"/>
       <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
+      <c r="C134" s="31"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
     </row>
     <row r="135" spans="1:5" ht="18" customHeight="1">
-      <c r="A135" s="1"/>
+      <c r="A135" s="26"/>
       <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
+      <c r="C135" s="31"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5" ht="18" customHeight="1">
-      <c r="A136" s="1"/>
+      <c r="A136" s="26"/>
       <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
+      <c r="C136" s="31"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
     </row>
     <row r="137" spans="1:5" ht="18" customHeight="1">
-      <c r="A137" s="1"/>
+      <c r="A137" s="26"/>
       <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
+      <c r="C137" s="31"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
     </row>
     <row r="138" spans="1:5" ht="18" customHeight="1">
-      <c r="A138" s="1"/>
+      <c r="A138" s="26"/>
       <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
+      <c r="C138" s="31"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
     </row>
     <row r="139" spans="1:5" ht="18" customHeight="1">
-      <c r="A139" s="1"/>
+      <c r="A139" s="26"/>
       <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
+      <c r="C139" s="31"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
     </row>
     <row r="140" spans="1:5" ht="18" customHeight="1">
-      <c r="A140" s="1"/>
+      <c r="A140" s="26"/>
       <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
+      <c r="C140" s="31"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
     </row>
     <row r="141" spans="1:5" ht="18" customHeight="1">
-      <c r="A141" s="1"/>
+      <c r="A141" s="26"/>
       <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
+      <c r="C141" s="31"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
     </row>
     <row r="142" spans="1:5" ht="18" customHeight="1">
-      <c r="A142" s="1"/>
+      <c r="A142" s="26"/>
       <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
+      <c r="C142" s="31"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
     </row>
     <row r="143" spans="1:5" ht="18" customHeight="1">
-      <c r="A143" s="1"/>
+      <c r="A143" s="26"/>
       <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
+      <c r="C143" s="31"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
     </row>
     <row r="144" spans="1:5" ht="18" customHeight="1">
-      <c r="A144" s="1"/>
+      <c r="A144" s="26"/>
       <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
+      <c r="C144" s="31"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
     </row>
     <row r="145" spans="1:5" ht="18" customHeight="1">
-      <c r="A145" s="1"/>
+      <c r="A145" s="26"/>
       <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
+      <c r="C145" s="31"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
     </row>
     <row r="146" spans="1:5" ht="18" customHeight="1">
-      <c r="A146" s="1"/>
+      <c r="A146" s="26"/>
       <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
+      <c r="C146" s="31"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
     </row>
     <row r="147" spans="1:5" ht="18" customHeight="1">
-      <c r="A147" s="1"/>
+      <c r="A147" s="26"/>
       <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
+      <c r="C147" s="31"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
     </row>
     <row r="148" spans="1:5" ht="18" customHeight="1">
-      <c r="A148" s="1"/>
+      <c r="A148" s="26"/>
       <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
+      <c r="C148" s="31"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
     </row>
     <row r="149" spans="1:5" ht="18" customHeight="1">
-      <c r="A149" s="1"/>
+      <c r="A149" s="26"/>
       <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
+      <c r="C149" s="31"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
     </row>
     <row r="150" spans="1:5" ht="18" customHeight="1">
-      <c r="A150" s="1"/>
+      <c r="A150" s="26"/>
       <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
+      <c r="C150" s="31"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
     </row>
     <row r="151" spans="1:5" ht="18" customHeight="1">
-      <c r="A151" s="1"/>
+      <c r="A151" s="26"/>
       <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
+      <c r="C151" s="31"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
     </row>
     <row r="152" spans="1:5" ht="18" customHeight="1">
-      <c r="A152" s="1"/>
+      <c r="A152" s="26"/>
       <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
+      <c r="C152" s="31"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
     </row>
     <row r="153" spans="1:5" ht="18" customHeight="1">
-      <c r="A153" s="1"/>
+      <c r="A153" s="26"/>
       <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
+      <c r="C153" s="31"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
     </row>
     <row r="154" spans="1:5" ht="18" customHeight="1">
-      <c r="A154" s="1"/>
+      <c r="A154" s="26"/>
       <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
+      <c r="C154" s="31"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
     </row>
     <row r="155" spans="1:5" ht="18" customHeight="1">
-      <c r="A155" s="1"/>
+      <c r="A155" s="26"/>
       <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
+      <c r="C155" s="31"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
     </row>
     <row r="156" spans="1:5" ht="18" customHeight="1">
-      <c r="A156" s="1"/>
+      <c r="A156" s="26"/>
       <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
+      <c r="C156" s="31"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
     </row>
     <row r="157" spans="1:5" ht="18" customHeight="1">
-      <c r="A157" s="1"/>
+      <c r="A157" s="26"/>
       <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
+      <c r="C157" s="31"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
     </row>
     <row r="158" spans="1:5" ht="18" customHeight="1">
-      <c r="A158" s="1"/>
+      <c r="A158" s="26"/>
       <c r="B158" s="2"/>
-      <c r="C158" s="2"/>
+      <c r="C158" s="31"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
     </row>
@@ -3411,1175 +3523,1175 @@
   <dimension ref="A1:E158"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.0625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="20.8125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="20.25" style="8" customWidth="1"/>
-    <col min="4" max="4" width="23.375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="16.0625" style="34" customWidth="1"/>
+    <col min="2" max="2" width="20.8125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="7" customWidth="1"/>
+    <col min="4" max="4" width="23.375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16.25" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="20"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="13"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="11"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="13"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
-      <c r="A8" s="13"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
-      <c r="A9" s="13"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
-      <c r="A10" s="13"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
-      <c r="A12" s="13"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1">
-      <c r="A13" s="13"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1">
-      <c r="A14" s="13"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1">
-      <c r="A15" s="13"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="13"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
-      <c r="A17" s="13"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
-      <c r="A18" s="13"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
-      <c r="A19" s="13"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
-      <c r="A20" s="13"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
-      <c r="A21" s="13"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1">
-      <c r="A22" s="13"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1">
-      <c r="A23" s="13"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1">
-      <c r="A24" s="13"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="13"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1">
-      <c r="A26" s="13"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1">
-      <c r="A27" s="13"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1">
-      <c r="A28" s="13"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1">
-      <c r="A29" s="13"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1">
-      <c r="A30" s="13"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="13"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1">
-      <c r="A32" s="13"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1">
-      <c r="A33" s="13"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1">
-      <c r="A34" s="13"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="13"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1">
-      <c r="A36" s="13"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1">
-      <c r="A37" s="13"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1">
-      <c r="A38" s="13"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1">
-      <c r="A39" s="13"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1">
-      <c r="A40" s="13"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1">
-      <c r="A41" s="13"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1">
-      <c r="A42" s="13"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
+      <c r="A42" s="24"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1">
-      <c r="A43" s="13"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1">
-      <c r="A44" s="13"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
+      <c r="A44" s="24"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1">
-      <c r="A45" s="13"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1">
-      <c r="A46" s="13"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
+      <c r="A46" s="24"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1">
-      <c r="A47" s="13"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
+      <c r="A47" s="24"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1">
-      <c r="A48" s="13"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1">
-      <c r="A49" s="13"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
+      <c r="A49" s="24"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1">
-      <c r="A50" s="13"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
+      <c r="A50" s="24"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1">
-      <c r="A51" s="13"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1">
-      <c r="A52" s="13"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
     </row>
     <row r="53" spans="1:5" ht="18" customHeight="1">
-      <c r="A53" s="13"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
+      <c r="A53" s="24"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1">
-      <c r="A54" s="13"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
+      <c r="A54" s="24"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1">
-      <c r="A55" s="13"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
+      <c r="A55" s="24"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1">
-      <c r="A56" s="13"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
+      <c r="A56" s="24"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1">
-      <c r="A57" s="13"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
+      <c r="A57" s="24"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1">
-      <c r="A58" s="13"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
+      <c r="A58" s="24"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
     </row>
     <row r="59" spans="1:5" ht="18" customHeight="1">
-      <c r="A59" s="13"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
+      <c r="A59" s="24"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1">
-      <c r="A60" s="13"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
+      <c r="A60" s="24"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1">
-      <c r="A61" s="13"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
+      <c r="A61" s="24"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1">
-      <c r="A62" s="13"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
+      <c r="A62" s="24"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1">
-      <c r="A63" s="13"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
+      <c r="A63" s="24"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1">
-      <c r="A64" s="13"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
+      <c r="A64" s="24"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
     </row>
     <row r="65" spans="1:5" ht="18" customHeight="1">
-      <c r="A65" s="13"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
+      <c r="A65" s="24"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
     </row>
     <row r="66" spans="1:5" ht="18" customHeight="1">
-      <c r="A66" s="13"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
+      <c r="A66" s="24"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
     </row>
     <row r="67" spans="1:5" ht="18" customHeight="1">
-      <c r="A67" s="13"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
+      <c r="A67" s="24"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
     </row>
     <row r="68" spans="1:5" ht="18" customHeight="1">
-      <c r="A68" s="13"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
+      <c r="A68" s="24"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
     </row>
     <row r="69" spans="1:5" ht="18" customHeight="1">
-      <c r="A69" s="13"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
+      <c r="A69" s="24"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
     </row>
     <row r="70" spans="1:5" ht="18" customHeight="1">
-      <c r="A70" s="13"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
+      <c r="A70" s="24"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
     </row>
     <row r="71" spans="1:5" ht="18" customHeight="1">
-      <c r="A71" s="13"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
+      <c r="A71" s="24"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
     </row>
     <row r="72" spans="1:5" ht="18" customHeight="1">
-      <c r="A72" s="13"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
+      <c r="A72" s="24"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
     </row>
     <row r="73" spans="1:5" ht="18" customHeight="1">
-      <c r="A73" s="13"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
+      <c r="A73" s="24"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
     </row>
     <row r="74" spans="1:5" ht="18" customHeight="1">
-      <c r="A74" s="13"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
+      <c r="A74" s="24"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
     </row>
     <row r="75" spans="1:5" ht="18" customHeight="1">
-      <c r="A75" s="13"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
+      <c r="A75" s="24"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
     </row>
     <row r="76" spans="1:5" ht="18" customHeight="1">
-      <c r="A76" s="13"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
+      <c r="A76" s="24"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
     </row>
     <row r="77" spans="1:5" ht="18" customHeight="1">
-      <c r="A77" s="13"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
+      <c r="A77" s="24"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
     </row>
     <row r="78" spans="1:5" ht="18" customHeight="1">
-      <c r="A78" s="13"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
+      <c r="A78" s="24"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
     </row>
     <row r="79" spans="1:5" ht="18" customHeight="1">
-      <c r="A79" s="13"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
+      <c r="A79" s="24"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
     </row>
     <row r="80" spans="1:5" ht="18" customHeight="1">
-      <c r="A80" s="13"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
+      <c r="A80" s="24"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
     </row>
     <row r="81" spans="1:5" ht="18" customHeight="1">
-      <c r="A81" s="13"/>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
+      <c r="A81" s="24"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
     </row>
     <row r="82" spans="1:5" ht="18" customHeight="1">
-      <c r="A82" s="13"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
+      <c r="A82" s="24"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
     </row>
     <row r="83" spans="1:5" ht="18" customHeight="1">
-      <c r="A83" s="13"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
+      <c r="A83" s="24"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
     </row>
     <row r="84" spans="1:5" ht="18" customHeight="1">
-      <c r="A84" s="13"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
     </row>
     <row r="85" spans="1:5" ht="18" customHeight="1">
-      <c r="A85" s="13"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
+      <c r="A85" s="24"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
     </row>
     <row r="86" spans="1:5" ht="18" customHeight="1">
-      <c r="A86" s="13"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
+      <c r="A86" s="24"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
     </row>
     <row r="87" spans="1:5" ht="18" customHeight="1">
-      <c r="A87" s="13"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
+      <c r="A87" s="24"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
     </row>
     <row r="88" spans="1:5" ht="18" customHeight="1">
-      <c r="A88" s="13"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
+      <c r="A88" s="24"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
     </row>
     <row r="89" spans="1:5" ht="18" customHeight="1">
-      <c r="A89" s="13"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
+      <c r="A89" s="24"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
     </row>
     <row r="90" spans="1:5" ht="18" customHeight="1">
-      <c r="A90" s="13"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
+      <c r="A90" s="24"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
     </row>
     <row r="91" spans="1:5" ht="18" customHeight="1">
-      <c r="A91" s="13"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
+      <c r="A91" s="24"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
     </row>
     <row r="92" spans="1:5" ht="18" customHeight="1">
-      <c r="A92" s="13"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
+      <c r="A92" s="24"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
     </row>
     <row r="93" spans="1:5" ht="18" customHeight="1">
-      <c r="A93" s="13"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
+      <c r="A93" s="24"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
     </row>
     <row r="94" spans="1:5" ht="18" customHeight="1">
-      <c r="A94" s="13"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
+      <c r="A94" s="24"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
     </row>
     <row r="95" spans="1:5" ht="18" customHeight="1">
-      <c r="A95" s="13"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
+      <c r="A95" s="24"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
     </row>
     <row r="96" spans="1:5" ht="18" customHeight="1">
-      <c r="A96" s="13"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
+      <c r="A96" s="24"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
     </row>
     <row r="97" spans="1:5" ht="18" customHeight="1">
-      <c r="A97" s="13"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
+      <c r="A97" s="24"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
     </row>
     <row r="98" spans="1:5" ht="18" customHeight="1">
-      <c r="A98" s="13"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
+      <c r="A98" s="24"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
     </row>
     <row r="99" spans="1:5" ht="18" customHeight="1">
-      <c r="A99" s="13"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
+      <c r="A99" s="24"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
     </row>
     <row r="100" spans="1:5" ht="18" customHeight="1">
-      <c r="A100" s="13"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
+      <c r="A100" s="24"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
     </row>
     <row r="101" spans="1:5" ht="18" customHeight="1">
-      <c r="A101" s="13"/>
-      <c r="B101" s="11"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
+      <c r="A101" s="24"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
     </row>
     <row r="102" spans="1:5" ht="18" customHeight="1">
-      <c r="A102" s="13"/>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
+      <c r="A102" s="24"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
     </row>
     <row r="103" spans="1:5" ht="18" customHeight="1">
-      <c r="A103" s="13"/>
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
+      <c r="A103" s="24"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
     </row>
     <row r="104" spans="1:5" ht="18" customHeight="1">
-      <c r="A104" s="13"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="11"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
+      <c r="A104" s="24"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
     </row>
     <row r="105" spans="1:5" ht="18" customHeight="1">
-      <c r="A105" s="13"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13"/>
+      <c r="A105" s="24"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
     </row>
     <row r="106" spans="1:5" ht="18" customHeight="1">
-      <c r="A106" s="13"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
+      <c r="A106" s="24"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
     </row>
     <row r="107" spans="1:5" ht="18" customHeight="1">
-      <c r="A107" s="13"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
+      <c r="A107" s="24"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
     </row>
     <row r="108" spans="1:5" ht="18" customHeight="1">
-      <c r="A108" s="13"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
+      <c r="A108" s="24"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
     </row>
     <row r="109" spans="1:5" ht="18" customHeight="1">
-      <c r="A109" s="13"/>
-      <c r="B109" s="11"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
+      <c r="A109" s="24"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
     </row>
     <row r="110" spans="1:5" ht="18" customHeight="1">
-      <c r="A110" s="13"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
+      <c r="A110" s="24"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
     </row>
     <row r="111" spans="1:5" ht="18" customHeight="1">
-      <c r="A111" s="13"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
+      <c r="A111" s="24"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
     </row>
     <row r="112" spans="1:5" ht="18" customHeight="1">
-      <c r="A112" s="13"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
+      <c r="A112" s="24"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
     </row>
     <row r="113" spans="1:5" ht="18" customHeight="1">
-      <c r="A113" s="13"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
+      <c r="A113" s="24"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="11"/>
+      <c r="E113" s="11"/>
     </row>
     <row r="114" spans="1:5" ht="18" customHeight="1">
-      <c r="A114" s="13"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
+      <c r="A114" s="24"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
     </row>
     <row r="115" spans="1:5" ht="18" customHeight="1">
-      <c r="A115" s="13"/>
-      <c r="B115" s="11"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="13"/>
-      <c r="E115" s="13"/>
+      <c r="A115" s="24"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
     </row>
     <row r="116" spans="1:5" ht="18" customHeight="1">
-      <c r="A116" s="13"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="13"/>
-      <c r="E116" s="13"/>
+      <c r="A116" s="24"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
     </row>
     <row r="117" spans="1:5" ht="18" customHeight="1">
-      <c r="A117" s="13"/>
-      <c r="B117" s="11"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="13"/>
-      <c r="E117" s="13"/>
+      <c r="A117" s="24"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="11"/>
+      <c r="E117" s="11"/>
     </row>
     <row r="118" spans="1:5" ht="18" customHeight="1">
-      <c r="A118" s="13"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="13"/>
-      <c r="E118" s="13"/>
+      <c r="A118" s="24"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
     </row>
     <row r="119" spans="1:5" ht="18" customHeight="1">
-      <c r="A119" s="13"/>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
+      <c r="A119" s="24"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
     </row>
     <row r="120" spans="1:5" ht="18" customHeight="1">
-      <c r="A120" s="13"/>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
+      <c r="A120" s="24"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
     </row>
     <row r="121" spans="1:5" ht="18" customHeight="1">
-      <c r="A121" s="13"/>
-      <c r="B121" s="11"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13"/>
+      <c r="A121" s="24"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
     </row>
     <row r="122" spans="1:5" ht="18" customHeight="1">
-      <c r="A122" s="13"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
+      <c r="A122" s="24"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="11"/>
+      <c r="E122" s="11"/>
     </row>
     <row r="123" spans="1:5" ht="18" customHeight="1">
-      <c r="A123" s="13"/>
-      <c r="B123" s="11"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="13"/>
-      <c r="E123" s="13"/>
+      <c r="A123" s="24"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
     </row>
     <row r="124" spans="1:5" ht="18" customHeight="1">
-      <c r="A124" s="13"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
+      <c r="A124" s="24"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
     </row>
     <row r="125" spans="1:5" ht="18" customHeight="1">
-      <c r="A125" s="13"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="13"/>
-      <c r="E125" s="13"/>
+      <c r="A125" s="24"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
     </row>
     <row r="126" spans="1:5" ht="18" customHeight="1">
-      <c r="A126" s="13"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
+      <c r="A126" s="24"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
     </row>
     <row r="127" spans="1:5" ht="18" customHeight="1">
-      <c r="A127" s="13"/>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="13"/>
-      <c r="E127" s="13"/>
+      <c r="A127" s="24"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
     </row>
     <row r="128" spans="1:5" ht="18" customHeight="1">
-      <c r="A128" s="13"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="13"/>
-      <c r="E128" s="13"/>
+      <c r="A128" s="24"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
     </row>
     <row r="129" spans="1:5" ht="18" customHeight="1">
-      <c r="A129" s="13"/>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="13"/>
-      <c r="E129" s="13"/>
+      <c r="A129" s="24"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
     </row>
     <row r="130" spans="1:5" ht="18" customHeight="1">
-      <c r="A130" s="13"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="13"/>
-      <c r="E130" s="13"/>
+      <c r="A130" s="24"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
     </row>
     <row r="131" spans="1:5" ht="18" customHeight="1">
-      <c r="A131" s="13"/>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="13"/>
-      <c r="E131" s="13"/>
+      <c r="A131" s="24"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
     </row>
     <row r="132" spans="1:5" ht="18" customHeight="1">
-      <c r="A132" s="13"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="13"/>
-      <c r="E132" s="13"/>
+      <c r="A132" s="24"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
     </row>
     <row r="133" spans="1:5" ht="18" customHeight="1">
-      <c r="A133" s="13"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="13"/>
-      <c r="E133" s="13"/>
+      <c r="A133" s="24"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
     </row>
     <row r="134" spans="1:5" ht="18" customHeight="1">
-      <c r="A134" s="13"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
+      <c r="A134" s="24"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
     </row>
     <row r="135" spans="1:5" ht="18" customHeight="1">
-      <c r="A135" s="13"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="13"/>
-      <c r="E135" s="13"/>
+      <c r="A135" s="24"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="11"/>
+      <c r="E135" s="11"/>
     </row>
     <row r="136" spans="1:5" ht="18" customHeight="1">
-      <c r="A136" s="13"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="13"/>
-      <c r="E136" s="13"/>
+      <c r="A136" s="24"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
     </row>
     <row r="137" spans="1:5" ht="18" customHeight="1">
-      <c r="A137" s="13"/>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="13"/>
-      <c r="E137" s="13"/>
+      <c r="A137" s="24"/>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
     </row>
     <row r="138" spans="1:5" ht="18" customHeight="1">
-      <c r="A138" s="13"/>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="13"/>
-      <c r="E138" s="13"/>
+      <c r="A138" s="24"/>
+      <c r="B138" s="9"/>
+      <c r="C138" s="9"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
     </row>
     <row r="139" spans="1:5" ht="18" customHeight="1">
-      <c r="A139" s="13"/>
-      <c r="B139" s="11"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="13"/>
-      <c r="E139" s="13"/>
+      <c r="A139" s="24"/>
+      <c r="B139" s="9"/>
+      <c r="C139" s="9"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
     </row>
     <row r="140" spans="1:5" ht="18" customHeight="1">
-      <c r="A140" s="13"/>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="13"/>
-      <c r="E140" s="13"/>
+      <c r="A140" s="24"/>
+      <c r="B140" s="9"/>
+      <c r="C140" s="9"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
     </row>
     <row r="141" spans="1:5" ht="18" customHeight="1">
-      <c r="A141" s="13"/>
-      <c r="B141" s="11"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="13"/>
-      <c r="E141" s="13"/>
+      <c r="A141" s="24"/>
+      <c r="B141" s="9"/>
+      <c r="C141" s="9"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
     </row>
     <row r="142" spans="1:5" ht="18" customHeight="1">
-      <c r="A142" s="13"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="13"/>
-      <c r="E142" s="13"/>
+      <c r="A142" s="24"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
     </row>
     <row r="143" spans="1:5" ht="18" customHeight="1">
-      <c r="A143" s="13"/>
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="13"/>
-      <c r="E143" s="13"/>
+      <c r="A143" s="24"/>
+      <c r="B143" s="9"/>
+      <c r="C143" s="9"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
     </row>
     <row r="144" spans="1:5" ht="18" customHeight="1">
-      <c r="A144" s="13"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="13"/>
-      <c r="E144" s="13"/>
+      <c r="A144" s="24"/>
+      <c r="B144" s="9"/>
+      <c r="C144" s="9"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
     </row>
     <row r="145" spans="1:5" ht="18" customHeight="1">
-      <c r="A145" s="13"/>
-      <c r="B145" s="11"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="13"/>
-      <c r="E145" s="13"/>
+      <c r="A145" s="24"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="9"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
     </row>
     <row r="146" spans="1:5" ht="18" customHeight="1">
-      <c r="A146" s="13"/>
-      <c r="B146" s="11"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="13"/>
-      <c r="E146" s="13"/>
+      <c r="A146" s="24"/>
+      <c r="B146" s="9"/>
+      <c r="C146" s="9"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
     </row>
     <row r="147" spans="1:5" ht="18" customHeight="1">
-      <c r="A147" s="13"/>
-      <c r="B147" s="11"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="13"/>
-      <c r="E147" s="13"/>
+      <c r="A147" s="24"/>
+      <c r="B147" s="9"/>
+      <c r="C147" s="9"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
     </row>
     <row r="148" spans="1:5" ht="18" customHeight="1">
-      <c r="A148" s="13"/>
-      <c r="B148" s="11"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="13"/>
-      <c r="E148" s="13"/>
+      <c r="A148" s="24"/>
+      <c r="B148" s="9"/>
+      <c r="C148" s="9"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
     </row>
     <row r="149" spans="1:5" ht="18" customHeight="1">
-      <c r="A149" s="13"/>
-      <c r="B149" s="11"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="13"/>
-      <c r="E149" s="13"/>
+      <c r="A149" s="24"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="9"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
     </row>
     <row r="150" spans="1:5" ht="18" customHeight="1">
-      <c r="A150" s="13"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="11"/>
-      <c r="D150" s="13"/>
-      <c r="E150" s="13"/>
+      <c r="A150" s="24"/>
+      <c r="B150" s="9"/>
+      <c r="C150" s="9"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
     </row>
     <row r="151" spans="1:5" ht="18" customHeight="1">
-      <c r="A151" s="13"/>
-      <c r="B151" s="11"/>
-      <c r="C151" s="11"/>
-      <c r="D151" s="13"/>
-      <c r="E151" s="13"/>
+      <c r="A151" s="24"/>
+      <c r="B151" s="9"/>
+      <c r="C151" s="9"/>
+      <c r="D151" s="11"/>
+      <c r="E151" s="11"/>
     </row>
     <row r="152" spans="1:5" ht="18" customHeight="1">
-      <c r="A152" s="13"/>
-      <c r="B152" s="11"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="13"/>
-      <c r="E152" s="13"/>
+      <c r="A152" s="24"/>
+      <c r="B152" s="9"/>
+      <c r="C152" s="9"/>
+      <c r="D152" s="11"/>
+      <c r="E152" s="11"/>
     </row>
     <row r="153" spans="1:5" ht="18" customHeight="1">
-      <c r="A153" s="13"/>
-      <c r="B153" s="11"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="13"/>
-      <c r="E153" s="13"/>
+      <c r="A153" s="24"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
     </row>
     <row r="154" spans="1:5" ht="18" customHeight="1">
-      <c r="A154" s="13"/>
-      <c r="B154" s="11"/>
-      <c r="C154" s="11"/>
-      <c r="D154" s="13"/>
-      <c r="E154" s="13"/>
+      <c r="A154" s="24"/>
+      <c r="B154" s="9"/>
+      <c r="C154" s="9"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
     </row>
     <row r="155" spans="1:5" ht="18" customHeight="1">
-      <c r="A155" s="13"/>
-      <c r="B155" s="11"/>
-      <c r="C155" s="11"/>
-      <c r="D155" s="13"/>
-      <c r="E155" s="13"/>
+      <c r="A155" s="24"/>
+      <c r="B155" s="9"/>
+      <c r="C155" s="9"/>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
     </row>
     <row r="156" spans="1:5" ht="18" customHeight="1">
-      <c r="A156" s="13"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="13"/>
-      <c r="E156" s="13"/>
+      <c r="A156" s="24"/>
+      <c r="B156" s="9"/>
+      <c r="C156" s="9"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
     </row>
     <row r="157" spans="1:5" ht="18" customHeight="1">
-      <c r="A157" s="13"/>
-      <c r="B157" s="11"/>
-      <c r="C157" s="11"/>
-      <c r="D157" s="13"/>
-      <c r="E157" s="13"/>
+      <c r="A157" s="24"/>
+      <c r="B157" s="9"/>
+      <c r="C157" s="9"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
     </row>
     <row r="158" spans="1:5" ht="18" customHeight="1">
-      <c r="A158" s="13"/>
-      <c r="B158" s="11"/>
-      <c r="C158" s="11"/>
-      <c r="D158" s="13"/>
-      <c r="E158" s="13"/>
+      <c r="A158" s="24"/>
+      <c r="B158" s="9"/>
+      <c r="C158" s="9"/>
+      <c r="D158" s="11"/>
+      <c r="E158" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4594,2697 +4706,2697 @@
   <dimension ref="A1:E158"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="16.0625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="15.25" style="8" customWidth="1"/>
-    <col min="3" max="3" width="13" style="8" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="8" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="16.0625" style="34" customWidth="1"/>
+    <col min="2" max="2" width="15.25" style="38" customWidth="1"/>
+    <col min="3" max="3" width="13" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16.25" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="16" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="37">
         <v>45292</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="9">
         <v>45298</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="37">
         <v>45299</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="9">
         <v>45305</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="37">
         <v>45306</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="9">
         <v>45312</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="37">
         <v>45313</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <v>45319</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="37">
         <v>45320</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <v>45326</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="37">
         <v>45327</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <v>45333</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="37">
         <v>45334</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <v>45340</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="37">
         <v>45341</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="9">
         <v>45347</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="37">
         <v>45348</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <v>45354</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="37">
         <v>45355</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <v>45361</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="37">
         <v>45362</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="9">
         <v>45368</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="37">
         <v>45369</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="9">
         <v>45375</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="37">
         <v>45376</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="9">
         <v>45382</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="37">
         <v>45383</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="9">
         <v>45389</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="37">
         <v>45390</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="9">
         <v>45396</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="37">
         <v>45397</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="9">
         <v>45403</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="37">
         <v>45404</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="9">
         <v>45410</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="37">
         <v>45411</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="9">
         <v>45417</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="37">
         <v>45418</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="9">
         <v>45424</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="37">
         <v>45425</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="9">
         <v>45431</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="37">
         <v>45432</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="9">
         <v>45438</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="37">
         <v>45439</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="9">
         <v>45445</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="37">
         <v>45446</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="9">
         <v>45452</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="37">
         <v>45453</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="9">
         <v>45459</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="37">
         <v>45460</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="9">
         <v>45466</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="37">
         <v>45467</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="9">
         <v>45473</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="37">
         <v>45474</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="9">
         <v>45480</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="37">
         <v>45481</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="9">
         <v>45487</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="37">
         <v>45488</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="9">
         <v>45494</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="37">
         <v>45495</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="9">
         <v>45501</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="37">
         <v>45502</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="9">
         <v>45508</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="37">
         <v>45509</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="9">
         <v>45515</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="37">
         <v>45516</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="9">
         <v>45522</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="37">
         <v>45523</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="9">
         <v>45529</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="37">
         <v>45530</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="9">
         <v>45536</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="37">
         <v>45537</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="9">
         <v>45543</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="37">
         <v>45544</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="9">
         <v>45550</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="37">
         <v>45551</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="9">
         <v>45557</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="37">
         <v>45558</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="9">
         <v>45564</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="37">
         <v>45565</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="9">
         <v>45571</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="37">
         <v>45572</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="9">
         <v>45578</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="37">
         <v>45579</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="9">
         <v>45585</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="37">
         <v>45586</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="9">
         <v>45592</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="37">
         <v>45593</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="9">
         <v>45599</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="37">
         <v>45600</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="9">
         <v>45606</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="37">
         <v>45607</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="9">
         <v>45613</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="37">
         <v>45614</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="9">
         <v>45620</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="37">
         <v>45621</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="9">
         <v>45627</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="37">
         <v>45628</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="9">
         <v>45634</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E50" s="13">
+      <c r="E50" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="37">
         <v>45635</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="9">
         <v>45641</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E51" s="13">
+      <c r="E51" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="37">
         <v>45642</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="9">
         <v>45648</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E52" s="13">
+      <c r="E52" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="18" customHeight="1">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="37">
         <v>45649</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="9">
         <v>45655</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="11">
         <v>2024</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="B54" s="11">
+      <c r="B54" s="37">
         <v>45656</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="9">
         <v>45662</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E54" s="13">
+      <c r="E54" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="37">
         <v>45663</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="9">
         <v>45669</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E55" s="13">
+      <c r="E55" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="37">
         <v>45670</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="9">
         <v>45676</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E56" s="13">
+      <c r="E56" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="37">
         <v>45677</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="9">
         <v>45683</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B58" s="11">
+      <c r="B58" s="37">
         <v>45684</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="9">
         <v>45690</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="18" customHeight="1">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="37">
         <v>45691</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="9">
         <v>45697</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E59" s="13">
+      <c r="E59" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="37">
         <v>45698</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="9">
         <v>45704</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E60" s="13">
+      <c r="E60" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="37">
         <v>45705</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="9">
         <v>45711</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E61" s="13">
+      <c r="E61" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B62" s="37">
         <v>45712</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="9">
         <v>45718</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D62" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E62" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="37">
         <v>45719</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="9">
         <v>45725</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E63" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="37">
         <v>45726</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C64" s="9">
         <v>45732</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E64" s="13">
+      <c r="E64" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="18" customHeight="1">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="37">
         <v>45733</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="9">
         <v>45739</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="18" customHeight="1">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="37">
         <v>45740</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C66" s="9">
         <v>45746</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="18" customHeight="1">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="37">
         <v>45747</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="9">
         <v>45753</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D67" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E67" s="13">
+      <c r="E67" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="18" customHeight="1">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="37">
         <v>45754</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="9">
         <v>45760</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E68" s="13">
+      <c r="E68" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="18" customHeight="1">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="37">
         <v>45761</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="9">
         <v>45767</v>
       </c>
-      <c r="D69" s="13" t="s">
+      <c r="D69" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="18" customHeight="1">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="B70" s="11">
+      <c r="B70" s="37">
         <v>45768</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="9">
         <v>45774</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="D70" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="18" customHeight="1">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="37">
         <v>45775</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="9">
         <v>45781</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="18" customHeight="1">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B72" s="11">
+      <c r="B72" s="37">
         <v>45782</v>
       </c>
-      <c r="C72" s="11">
+      <c r="C72" s="9">
         <v>45788</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="18" customHeight="1">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="37">
         <v>45789</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="9">
         <v>45795</v>
       </c>
-      <c r="D73" s="13" t="s">
+      <c r="D73" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="18" customHeight="1">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="B74" s="11">
+      <c r="B74" s="37">
         <v>45796</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="9">
         <v>45802</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="D74" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="18" customHeight="1">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="37">
         <v>45803</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="9">
         <v>45809</v>
       </c>
-      <c r="D75" s="13" t="s">
+      <c r="D75" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E75" s="13">
+      <c r="E75" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="18" customHeight="1">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="37">
         <v>45810</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="9">
         <v>45816</v>
       </c>
-      <c r="D76" s="13" t="s">
+      <c r="D76" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="18" customHeight="1">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="37">
         <v>45817</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="9">
         <v>45823</v>
       </c>
-      <c r="D77" s="13" t="s">
+      <c r="D77" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="18" customHeight="1">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="37">
         <v>45824</v>
       </c>
-      <c r="C78" s="11">
+      <c r="C78" s="9">
         <v>45830</v>
       </c>
-      <c r="D78" s="13" t="s">
+      <c r="D78" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="18" customHeight="1">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="37">
         <v>45831</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="9">
         <v>45837</v>
       </c>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="18" customHeight="1">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="37">
         <v>45838</v>
       </c>
-      <c r="C80" s="11">
+      <c r="C80" s="9">
         <v>45844</v>
       </c>
-      <c r="D80" s="13" t="s">
+      <c r="D80" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E80" s="13">
+      <c r="E80" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="18" customHeight="1">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="37">
         <v>45845</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="9">
         <v>45851</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="D81" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E81" s="13">
+      <c r="E81" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="18" customHeight="1">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="B82" s="11">
+      <c r="B82" s="37">
         <v>45852</v>
       </c>
-      <c r="C82" s="11">
+      <c r="C82" s="9">
         <v>45858</v>
       </c>
-      <c r="D82" s="13" t="s">
+      <c r="D82" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E82" s="13">
+      <c r="E82" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="18" customHeight="1">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="B83" s="11">
+      <c r="B83" s="37">
         <v>45859</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="9">
         <v>45865</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D83" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E83" s="13">
+      <c r="E83" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="18" customHeight="1">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="B84" s="11">
+      <c r="B84" s="37">
         <v>45866</v>
       </c>
-      <c r="C84" s="11">
+      <c r="C84" s="9">
         <v>45872</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E84" s="13">
+      <c r="E84" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="18" customHeight="1">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="B85" s="11">
+      <c r="B85" s="37">
         <v>45873</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="9">
         <v>45879</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="D85" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E85" s="13">
+      <c r="E85" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="18" customHeight="1">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="B86" s="11">
+      <c r="B86" s="37">
         <v>45880</v>
       </c>
-      <c r="C86" s="11">
+      <c r="C86" s="9">
         <v>45886</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E86" s="13">
+      <c r="E86" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="18" customHeight="1">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="B87" s="11">
+      <c r="B87" s="37">
         <v>45887</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="9">
         <v>45893</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E87" s="13">
+      <c r="E87" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="18" customHeight="1">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="B88" s="11">
+      <c r="B88" s="37">
         <v>45894</v>
       </c>
-      <c r="C88" s="11">
+      <c r="C88" s="9">
         <v>45900</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E88" s="13">
+      <c r="E88" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="18" customHeight="1">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B89" s="11">
+      <c r="B89" s="37">
         <v>45901</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="9">
         <v>45907</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E89" s="13">
+      <c r="E89" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="18" customHeight="1">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="B90" s="11">
+      <c r="B90" s="37">
         <v>45908</v>
       </c>
-      <c r="C90" s="11">
+      <c r="C90" s="9">
         <v>45914</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E90" s="13">
+      <c r="E90" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="18" customHeight="1">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B91" s="11">
+      <c r="B91" s="37">
         <v>45915</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="9">
         <v>45921</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E91" s="13">
+      <c r="E91" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="18" customHeight="1">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="11">
+      <c r="B92" s="37">
         <v>45922</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="9">
         <v>45928</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E92" s="13">
+      <c r="E92" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="18" customHeight="1">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="37">
         <v>45929</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="9">
         <v>45935</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D93" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E93" s="13">
+      <c r="E93" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="18" customHeight="1">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="B94" s="11">
+      <c r="B94" s="37">
         <v>45936</v>
       </c>
-      <c r="C94" s="11">
+      <c r="C94" s="9">
         <v>45942</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E94" s="13">
+      <c r="E94" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="18" customHeight="1">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="37">
         <v>45943</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="9">
         <v>45949</v>
       </c>
-      <c r="D95" s="13" t="s">
+      <c r="D95" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E95" s="13">
+      <c r="E95" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="18" customHeight="1">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B96" s="11">
+      <c r="B96" s="37">
         <v>45950</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="9">
         <v>45956</v>
       </c>
-      <c r="D96" s="13" t="s">
+      <c r="D96" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E96" s="13">
+      <c r="E96" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="18" customHeight="1">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="37">
         <v>45957</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="9">
         <v>45963</v>
       </c>
-      <c r="D97" s="13" t="s">
+      <c r="D97" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E97" s="13">
+      <c r="E97" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="18" customHeight="1">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B98" s="11">
+      <c r="B98" s="37">
         <v>45964</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="9">
         <v>45970</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E98" s="13">
+      <c r="E98" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="18" customHeight="1">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="37">
         <v>45971</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="9">
         <v>45977</v>
       </c>
-      <c r="D99" s="13" t="s">
+      <c r="D99" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E99" s="13">
+      <c r="E99" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="18" customHeight="1">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="B100" s="11">
+      <c r="B100" s="37">
         <v>45978</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="9">
         <v>45984</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E100" s="13">
+      <c r="E100" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="18" customHeight="1">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="37">
         <v>45985</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="9">
         <v>45991</v>
       </c>
-      <c r="D101" s="13" t="s">
+      <c r="D101" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E101" s="13">
+      <c r="E101" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="18" customHeight="1">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="B102" s="11">
+      <c r="B102" s="37">
         <v>45992</v>
       </c>
-      <c r="C102" s="11">
+      <c r="C102" s="9">
         <v>45998</v>
       </c>
-      <c r="D102" s="13" t="s">
+      <c r="D102" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E102" s="13">
+      <c r="E102" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="18" customHeight="1">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="37">
         <v>45999</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="9">
         <v>46005</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E103" s="13">
+      <c r="E103" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="18" customHeight="1">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="B104" s="11">
+      <c r="B104" s="37">
         <v>46006</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="9">
         <v>46012</v>
       </c>
-      <c r="D104" s="13" t="s">
+      <c r="D104" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E104" s="13">
+      <c r="E104" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="18" customHeight="1">
-      <c r="A105" s="13" t="s">
+      <c r="A105" s="24" t="s">
         <v>198</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="37">
         <v>46013</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="9">
         <v>46019</v>
       </c>
-      <c r="D105" s="13" t="s">
+      <c r="D105" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="E105" s="13">
+      <c r="E105" s="11">
         <v>2025</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="18" customHeight="1">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="B106" s="11">
+      <c r="B106" s="37">
         <v>46020</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="9">
         <v>46026</v>
       </c>
-      <c r="D106" s="13" t="s">
+      <c r="D106" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E106" s="13">
+      <c r="E106" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="18" customHeight="1">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="B107" s="11">
+      <c r="B107" s="37">
         <v>46027</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="9">
         <v>46033</v>
       </c>
-      <c r="D107" s="13" t="s">
+      <c r="D107" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E107" s="13">
+      <c r="E107" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="18" customHeight="1">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="B108" s="11">
+      <c r="B108" s="37">
         <v>46034</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="9">
         <v>46040</v>
       </c>
-      <c r="D108" s="13" t="s">
+      <c r="D108" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E108" s="13">
+      <c r="E108" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="18" customHeight="1">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="B109" s="11">
+      <c r="B109" s="37">
         <v>46041</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="9">
         <v>46047</v>
       </c>
-      <c r="D109" s="13" t="s">
+      <c r="D109" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E109" s="13">
+      <c r="E109" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="18" customHeight="1">
-      <c r="A110" s="13" t="s">
+      <c r="A110" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="B110" s="11">
+      <c r="B110" s="37">
         <v>46048</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="9">
         <v>46054</v>
       </c>
-      <c r="D110" s="13" t="s">
+      <c r="D110" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E110" s="13">
+      <c r="E110" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="18" customHeight="1">
-      <c r="A111" s="13" t="s">
+      <c r="A111" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="B111" s="11">
+      <c r="B111" s="37">
         <v>46055</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="9">
         <v>46061</v>
       </c>
-      <c r="D111" s="13" t="s">
+      <c r="D111" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E111" s="13">
+      <c r="E111" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="18" customHeight="1">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="B112" s="11">
+      <c r="B112" s="37">
         <v>46062</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="9">
         <v>46068</v>
       </c>
-      <c r="D112" s="13" t="s">
+      <c r="D112" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E112" s="13">
+      <c r="E112" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="18" customHeight="1">
-      <c r="A113" s="13" t="s">
+      <c r="A113" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="B113" s="11">
+      <c r="B113" s="37">
         <v>46069</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="9">
         <v>46075</v>
       </c>
-      <c r="D113" s="13" t="s">
+      <c r="D113" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E113" s="13">
+      <c r="E113" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="18" customHeight="1">
-      <c r="A114" s="13" t="s">
+      <c r="A114" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="B114" s="11">
+      <c r="B114" s="37">
         <v>46076</v>
       </c>
-      <c r="C114" s="11">
+      <c r="C114" s="9">
         <v>46082</v>
       </c>
-      <c r="D114" s="13" t="s">
+      <c r="D114" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E114" s="13">
+      <c r="E114" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="18" customHeight="1">
-      <c r="A115" s="13" t="s">
+      <c r="A115" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="B115" s="11">
+      <c r="B115" s="37">
         <v>46083</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="9">
         <v>46089</v>
       </c>
-      <c r="D115" s="13" t="s">
+      <c r="D115" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E115" s="13">
+      <c r="E115" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="18" customHeight="1">
-      <c r="A116" s="13" t="s">
+      <c r="A116" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="B116" s="11">
+      <c r="B116" s="37">
         <v>46090</v>
       </c>
-      <c r="C116" s="11">
+      <c r="C116" s="9">
         <v>46096</v>
       </c>
-      <c r="D116" s="13" t="s">
+      <c r="D116" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E116" s="13">
+      <c r="E116" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="18" customHeight="1">
-      <c r="A117" s="13" t="s">
+      <c r="A117" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="B117" s="11">
+      <c r="B117" s="37">
         <v>46097</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="9">
         <v>46103</v>
       </c>
-      <c r="D117" s="13" t="s">
+      <c r="D117" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E117" s="13">
+      <c r="E117" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="18" customHeight="1">
-      <c r="A118" s="13" t="s">
+      <c r="A118" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="B118" s="11">
+      <c r="B118" s="37">
         <v>46104</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="9">
         <v>46110</v>
       </c>
-      <c r="D118" s="13" t="s">
+      <c r="D118" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E118" s="13">
+      <c r="E118" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="18" customHeight="1">
-      <c r="A119" s="13" t="s">
+      <c r="A119" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="B119" s="11">
+      <c r="B119" s="37">
         <v>46111</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="9">
         <v>46117</v>
       </c>
-      <c r="D119" s="13" t="s">
+      <c r="D119" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E119" s="13">
+      <c r="E119" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="18" customHeight="1">
-      <c r="A120" s="13" t="s">
+      <c r="A120" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="B120" s="11">
+      <c r="B120" s="37">
         <v>46118</v>
       </c>
-      <c r="C120" s="11">
+      <c r="C120" s="9">
         <v>46124</v>
       </c>
-      <c r="D120" s="13" t="s">
+      <c r="D120" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E120" s="13">
+      <c r="E120" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="18" customHeight="1">
-      <c r="A121" s="13" t="s">
+      <c r="A121" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="B121" s="11">
+      <c r="B121" s="37">
         <v>46125</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="9">
         <v>46131</v>
       </c>
-      <c r="D121" s="13" t="s">
+      <c r="D121" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E121" s="13">
+      <c r="E121" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="18" customHeight="1">
-      <c r="A122" s="13" t="s">
+      <c r="A122" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="B122" s="11">
+      <c r="B122" s="37">
         <v>46132</v>
       </c>
-      <c r="C122" s="11">
+      <c r="C122" s="9">
         <v>46138</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D122" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E122" s="13">
+      <c r="E122" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="18" customHeight="1">
-      <c r="A123" s="13" t="s">
+      <c r="A123" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="B123" s="11">
+      <c r="B123" s="37">
         <v>46139</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="9">
         <v>46145</v>
       </c>
-      <c r="D123" s="13" t="s">
+      <c r="D123" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E123" s="13">
+      <c r="E123" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="18" customHeight="1">
-      <c r="A124" s="13" t="s">
+      <c r="A124" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="B124" s="11">
+      <c r="B124" s="37">
         <v>46146</v>
       </c>
-      <c r="C124" s="11">
+      <c r="C124" s="9">
         <v>46152</v>
       </c>
-      <c r="D124" s="13" t="s">
+      <c r="D124" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E124" s="13">
+      <c r="E124" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="18" customHeight="1">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="B125" s="11">
+      <c r="B125" s="37">
         <v>46153</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="9">
         <v>46159</v>
       </c>
-      <c r="D125" s="13" t="s">
+      <c r="D125" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E125" s="13">
+      <c r="E125" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="18" customHeight="1">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="B126" s="11">
+      <c r="B126" s="37">
         <v>46160</v>
       </c>
-      <c r="C126" s="11">
+      <c r="C126" s="9">
         <v>46166</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D126" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E126" s="13">
+      <c r="E126" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="18" customHeight="1">
-      <c r="A127" s="13" t="s">
+      <c r="A127" s="24" t="s">
         <v>222</v>
       </c>
-      <c r="B127" s="11">
+      <c r="B127" s="37">
         <v>46167</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="9">
         <v>46173</v>
       </c>
-      <c r="D127" s="13" t="s">
+      <c r="D127" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E127" s="13">
+      <c r="E127" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="18" customHeight="1">
-      <c r="A128" s="13" t="s">
+      <c r="A128" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="B128" s="11">
+      <c r="B128" s="37">
         <v>46174</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128" s="9">
         <v>46180</v>
       </c>
-      <c r="D128" s="13" t="s">
+      <c r="D128" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E128" s="13">
+      <c r="E128" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="18" customHeight="1">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="B129" s="11">
+      <c r="B129" s="37">
         <v>46181</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="9">
         <v>46187</v>
       </c>
-      <c r="D129" s="13" t="s">
+      <c r="D129" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E129" s="13">
+      <c r="E129" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="18" customHeight="1">
-      <c r="A130" s="13" t="s">
+      <c r="A130" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="B130" s="11">
+      <c r="B130" s="37">
         <v>46188</v>
       </c>
-      <c r="C130" s="11">
+      <c r="C130" s="9">
         <v>46194</v>
       </c>
-      <c r="D130" s="13" t="s">
+      <c r="D130" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E130" s="13">
+      <c r="E130" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="18" customHeight="1">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="B131" s="11">
+      <c r="B131" s="37">
         <v>46195</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="9">
         <v>46201</v>
       </c>
-      <c r="D131" s="13" t="s">
+      <c r="D131" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E131" s="13">
+      <c r="E131" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="18" customHeight="1">
-      <c r="A132" s="13" t="s">
+      <c r="A132" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="B132" s="11">
+      <c r="B132" s="37">
         <v>46202</v>
       </c>
-      <c r="C132" s="11">
+      <c r="C132" s="9">
         <v>46208</v>
       </c>
-      <c r="D132" s="13" t="s">
+      <c r="D132" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E132" s="13">
+      <c r="E132" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="18" customHeight="1">
-      <c r="A133" s="13" t="s">
+      <c r="A133" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="B133" s="11">
+      <c r="B133" s="37">
         <v>46209</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="9">
         <v>46215</v>
       </c>
-      <c r="D133" s="13" t="s">
+      <c r="D133" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E133" s="13">
+      <c r="E133" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="18" customHeight="1">
-      <c r="A134" s="13" t="s">
+      <c r="A134" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="B134" s="11">
+      <c r="B134" s="37">
         <v>46216</v>
       </c>
-      <c r="C134" s="11">
+      <c r="C134" s="9">
         <v>46222</v>
       </c>
-      <c r="D134" s="13" t="s">
+      <c r="D134" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E134" s="13">
+      <c r="E134" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="18" customHeight="1">
-      <c r="A135" s="13" t="s">
+      <c r="A135" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="B135" s="11">
+      <c r="B135" s="37">
         <v>46223</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="9">
         <v>46229</v>
       </c>
-      <c r="D135" s="13" t="s">
+      <c r="D135" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E135" s="13">
+      <c r="E135" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="18" customHeight="1">
-      <c r="A136" s="13" t="s">
+      <c r="A136" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="B136" s="11">
+      <c r="B136" s="37">
         <v>46230</v>
       </c>
-      <c r="C136" s="11">
+      <c r="C136" s="9">
         <v>46236</v>
       </c>
-      <c r="D136" s="13" t="s">
+      <c r="D136" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E136" s="13">
+      <c r="E136" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="18" customHeight="1">
-      <c r="A137" s="13" t="s">
+      <c r="A137" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B137" s="37">
         <v>46237</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="9">
         <v>46243</v>
       </c>
-      <c r="D137" s="13" t="s">
+      <c r="D137" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E137" s="13">
+      <c r="E137" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="18" customHeight="1">
-      <c r="A138" s="13" t="s">
+      <c r="A138" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="B138" s="11">
+      <c r="B138" s="37">
         <v>46244</v>
       </c>
-      <c r="C138" s="11">
+      <c r="C138" s="9">
         <v>46250</v>
       </c>
-      <c r="D138" s="13" t="s">
+      <c r="D138" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E138" s="13">
+      <c r="E138" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="18" customHeight="1">
-      <c r="A139" s="13" t="s">
+      <c r="A139" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="B139" s="11">
+      <c r="B139" s="37">
         <v>46251</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="9">
         <v>46257</v>
       </c>
-      <c r="D139" s="13" t="s">
+      <c r="D139" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E139" s="13">
+      <c r="E139" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="18" customHeight="1">
-      <c r="A140" s="13" t="s">
+      <c r="A140" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="B140" s="11">
+      <c r="B140" s="37">
         <v>46258</v>
       </c>
-      <c r="C140" s="11">
+      <c r="C140" s="9">
         <v>46264</v>
       </c>
-      <c r="D140" s="13" t="s">
+      <c r="D140" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E140" s="13">
+      <c r="E140" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="18" customHeight="1">
-      <c r="A141" s="13" t="s">
+      <c r="A141" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="B141" s="11">
+      <c r="B141" s="37">
         <v>46265</v>
       </c>
-      <c r="C141" s="11">
+      <c r="C141" s="9">
         <v>46271</v>
       </c>
-      <c r="D141" s="13" t="s">
+      <c r="D141" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E141" s="13">
+      <c r="E141" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="18" customHeight="1">
-      <c r="A142" s="13" t="s">
+      <c r="A142" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="B142" s="11">
+      <c r="B142" s="37">
         <v>46272</v>
       </c>
-      <c r="C142" s="11">
+      <c r="C142" s="9">
         <v>46278</v>
       </c>
-      <c r="D142" s="13" t="s">
+      <c r="D142" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E142" s="13">
+      <c r="E142" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="18" customHeight="1">
-      <c r="A143" s="13" t="s">
+      <c r="A143" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="B143" s="11">
+      <c r="B143" s="37">
         <v>46279</v>
       </c>
-      <c r="C143" s="11">
+      <c r="C143" s="9">
         <v>46285</v>
       </c>
-      <c r="D143" s="13" t="s">
+      <c r="D143" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E143" s="13">
+      <c r="E143" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="18" customHeight="1">
-      <c r="A144" s="13" t="s">
+      <c r="A144" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="B144" s="11">
+      <c r="B144" s="37">
         <v>46286</v>
       </c>
-      <c r="C144" s="11">
+      <c r="C144" s="9">
         <v>46292</v>
       </c>
-      <c r="D144" s="13" t="s">
+      <c r="D144" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E144" s="13">
+      <c r="E144" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="18" customHeight="1">
-      <c r="A145" s="13" t="s">
+      <c r="A145" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="B145" s="11">
+      <c r="B145" s="37">
         <v>46293</v>
       </c>
-      <c r="C145" s="11">
+      <c r="C145" s="9">
         <v>46299</v>
       </c>
-      <c r="D145" s="13" t="s">
+      <c r="D145" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E145" s="13">
+      <c r="E145" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="18" customHeight="1">
-      <c r="A146" s="13" t="s">
+      <c r="A146" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="B146" s="11">
+      <c r="B146" s="37">
         <v>46300</v>
       </c>
-      <c r="C146" s="11">
+      <c r="C146" s="9">
         <v>46306</v>
       </c>
-      <c r="D146" s="13" t="s">
+      <c r="D146" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E146" s="13">
+      <c r="E146" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="18" customHeight="1">
-      <c r="A147" s="13" t="s">
+      <c r="A147" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="B147" s="11">
+      <c r="B147" s="37">
         <v>46307</v>
       </c>
-      <c r="C147" s="11">
+      <c r="C147" s="9">
         <v>46313</v>
       </c>
-      <c r="D147" s="13" t="s">
+      <c r="D147" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E147" s="13">
+      <c r="E147" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="18" customHeight="1">
-      <c r="A148" s="13" t="s">
+      <c r="A148" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="B148" s="11">
+      <c r="B148" s="37">
         <v>46314</v>
       </c>
-      <c r="C148" s="11">
+      <c r="C148" s="9">
         <v>46320</v>
       </c>
-      <c r="D148" s="13" t="s">
+      <c r="D148" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E148" s="13">
+      <c r="E148" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="18" customHeight="1">
-      <c r="A149" s="13" t="s">
+      <c r="A149" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="B149" s="11">
+      <c r="B149" s="37">
         <v>46321</v>
       </c>
-      <c r="C149" s="11">
+      <c r="C149" s="9">
         <v>46327</v>
       </c>
-      <c r="D149" s="13" t="s">
+      <c r="D149" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E149" s="13">
+      <c r="E149" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="18" customHeight="1">
-      <c r="A150" s="13" t="s">
+      <c r="A150" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="B150" s="11">
+      <c r="B150" s="37">
         <v>46328</v>
       </c>
-      <c r="C150" s="11">
+      <c r="C150" s="9">
         <v>46334</v>
       </c>
-      <c r="D150" s="13" t="s">
+      <c r="D150" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E150" s="13">
+      <c r="E150" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="18" customHeight="1">
-      <c r="A151" s="13" t="s">
+      <c r="A151" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="B151" s="11">
+      <c r="B151" s="37">
         <v>46335</v>
       </c>
-      <c r="C151" s="11">
+      <c r="C151" s="9">
         <v>46341</v>
       </c>
-      <c r="D151" s="13" t="s">
+      <c r="D151" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E151" s="13">
+      <c r="E151" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="18" customHeight="1">
-      <c r="A152" s="13" t="s">
+      <c r="A152" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="B152" s="11">
+      <c r="B152" s="37">
         <v>46342</v>
       </c>
-      <c r="C152" s="11">
+      <c r="C152" s="9">
         <v>46348</v>
       </c>
-      <c r="D152" s="13" t="s">
+      <c r="D152" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E152" s="13">
+      <c r="E152" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="18" customHeight="1">
-      <c r="A153" s="13" t="s">
+      <c r="A153" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="B153" s="11">
+      <c r="B153" s="37">
         <v>46349</v>
       </c>
-      <c r="C153" s="11">
+      <c r="C153" s="9">
         <v>46355</v>
       </c>
-      <c r="D153" s="13" t="s">
+      <c r="D153" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E153" s="13">
+      <c r="E153" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="18" customHeight="1">
-      <c r="A154" s="13" t="s">
+      <c r="A154" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="B154" s="11">
+      <c r="B154" s="37">
         <v>46356</v>
       </c>
-      <c r="C154" s="11">
+      <c r="C154" s="9">
         <v>46362</v>
       </c>
-      <c r="D154" s="13" t="s">
+      <c r="D154" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E154" s="13">
+      <c r="E154" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="18" customHeight="1">
-      <c r="A155" s="13" t="s">
+      <c r="A155" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="B155" s="11">
+      <c r="B155" s="37">
         <v>46363</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C155" s="9">
         <v>46369</v>
       </c>
-      <c r="D155" s="13" t="s">
+      <c r="D155" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E155" s="13">
+      <c r="E155" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="18" customHeight="1">
-      <c r="A156" s="13" t="s">
+      <c r="A156" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="B156" s="11">
+      <c r="B156" s="37">
         <v>46370</v>
       </c>
-      <c r="C156" s="11">
+      <c r="C156" s="9">
         <v>46376</v>
       </c>
-      <c r="D156" s="13" t="s">
+      <c r="D156" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E156" s="13">
+      <c r="E156" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="18" customHeight="1">
-      <c r="A157" s="13" t="s">
+      <c r="A157" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="B157" s="11">
+      <c r="B157" s="37">
         <v>46377</v>
       </c>
-      <c r="C157" s="11">
+      <c r="C157" s="9">
         <v>46383</v>
       </c>
-      <c r="D157" s="13" t="s">
+      <c r="D157" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E157" s="13">
+      <c r="E157" s="11">
         <v>2026</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="18" customHeight="1">
-      <c r="A158" s="13" t="s">
+      <c r="A158" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="B158" s="11">
+      <c r="B158" s="37">
         <v>46384</v>
       </c>
-      <c r="C158" s="11">
+      <c r="C158" s="9">
         <v>46387</v>
       </c>
-      <c r="D158" s="13" t="s">
+      <c r="D158" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="E158" s="13">
+      <c r="E158" s="11">
         <v>2026</v>
       </c>
     </row>
